--- a/tts/voices.xlsx
+++ b/tts/voices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joelcespedes/Desktop/voices/tts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5FB4EB-CE90-1941-AD12-68F9113D9AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504677C7-7EA1-D848-B29E-9195823376C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="70880" yWindow="8160" windowWidth="31520" windowHeight="35040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="551">
   <si>
     <t>Who looks after your dog?</t>
   </si>
@@ -1019,6 +1019,660 @@
   </si>
   <si>
     <t>¿Desde qué estación sale el tren?</t>
+  </si>
+  <si>
+    <t>They agreed to work together.</t>
+  </si>
+  <si>
+    <t>Acordaron trabajar juntos.</t>
+  </si>
+  <si>
+    <t>Can you imagine living there?</t>
+  </si>
+  <si>
+    <t>¿Puedes imaginar vivir allí?</t>
+  </si>
+  <si>
+    <t>Did they find the problem?</t>
+  </si>
+  <si>
+    <t>¿Encontraron el problema?</t>
+  </si>
+  <si>
+    <t>I intend to study tonight.</t>
+  </si>
+  <si>
+    <t>Tengo intención de estudiar esta noche.</t>
+  </si>
+  <si>
+    <t>We would stay another week.</t>
+  </si>
+  <si>
+    <t>Nos quedaríamos otra semana.</t>
+  </si>
+  <si>
+    <t>The process involves checking every file.</t>
+  </si>
+  <si>
+    <t>El proceso implica revisar cada archivo.</t>
+  </si>
+  <si>
+    <t>We need to talk later.</t>
+  </si>
+  <si>
+    <t>Necesitamos hablar después.</t>
+  </si>
+  <si>
+    <t>They might cancel the meeting.</t>
+  </si>
+  <si>
+    <t>Podrían cancelar la reunión.</t>
+  </si>
+  <si>
+    <t>I can't afford to wait.</t>
+  </si>
+  <si>
+    <t>No puedo permitirme esperar.</t>
+  </si>
+  <si>
+    <t>They should arrive earlier.</t>
+  </si>
+  <si>
+    <t>Deberían llegar más temprano.</t>
+  </si>
+  <si>
+    <t>Do you mind waiting outside?</t>
+  </si>
+  <si>
+    <t>¿Te importa esperar afuera?</t>
+  </si>
+  <si>
+    <t>We hope to finish early.</t>
+  </si>
+  <si>
+    <t>Esperamos terminar temprano.</t>
+  </si>
+  <si>
+    <t>She might know the answer.</t>
+  </si>
+  <si>
+    <t>Puede que sepa la respuesta.</t>
+  </si>
+  <si>
+    <t>They postponed launching the product.</t>
+  </si>
+  <si>
+    <t>Pospusieron lanzar el producto.</t>
+  </si>
+  <si>
+    <t>She decided to study medicine.</t>
+  </si>
+  <si>
+    <t>Ella decidió estudiar medicina.</t>
+  </si>
+  <si>
+    <t>She practises writing short emails.</t>
+  </si>
+  <si>
+    <t>Ella practica escribir correos cortos.</t>
+  </si>
+  <si>
+    <t>We must leave immediately.</t>
+  </si>
+  <si>
+    <t>Debemos irnos inmediatamente.</t>
+  </si>
+  <si>
+    <t>Keep practising your English daily.</t>
+  </si>
+  <si>
+    <t>Sigue practicando tu inglés diariamente.</t>
+  </si>
+  <si>
+    <t>They must pay before Friday.</t>
+  </si>
+  <si>
+    <t>Deben pagar antes del viernes.</t>
+  </si>
+  <si>
+    <t>He seems to understand now.</t>
+  </si>
+  <si>
+    <t>Él parece entender ahora.</t>
+  </si>
+  <si>
+    <t>He admitted breaking the window.</t>
+  </si>
+  <si>
+    <t>Él admitió romper la ventana.</t>
+  </si>
+  <si>
+    <t>Will she join the meeting?</t>
+  </si>
+  <si>
+    <t>¿Ella se unirá a la reunión?</t>
+  </si>
+  <si>
+    <t>They can't afford to lose.</t>
+  </si>
+  <si>
+    <t>No pueden permitirse perder.</t>
+  </si>
+  <si>
+    <t>She quit smoking last year.</t>
+  </si>
+  <si>
+    <t>Do we need more time?</t>
+  </si>
+  <si>
+    <t>¿Necesitamos más tiempo?</t>
+  </si>
+  <si>
+    <t>She seems to know everything.</t>
+  </si>
+  <si>
+    <t>Ella parece saberlo todo.</t>
+  </si>
+  <si>
+    <t>Did she call you yesterday?</t>
+  </si>
+  <si>
+    <t>¿Ella te llamó ayer?</t>
+  </si>
+  <si>
+    <t>They refused to sign it.</t>
+  </si>
+  <si>
+    <t>Se negaron a firmarlo.</t>
+  </si>
+  <si>
+    <t>I appreciate you helping me.</t>
+  </si>
+  <si>
+    <t>Agradezco que me ayudes.</t>
+  </si>
+  <si>
+    <t>We prepared to leave early.</t>
+  </si>
+  <si>
+    <t>Nos preparamos para salir temprano.</t>
+  </si>
+  <si>
+    <t>You must finish this today.</t>
+  </si>
+  <si>
+    <t>Debes terminar esto hoy.</t>
+  </si>
+  <si>
+    <t>Consider changing your current plan.</t>
+  </si>
+  <si>
+    <t>Considera cambiar tu plan actual.</t>
+  </si>
+  <si>
+    <t>Does she speak English?</t>
+  </si>
+  <si>
+    <t>¿Ella habla inglés?</t>
+  </si>
+  <si>
+    <t>Imagine working without any meetings.</t>
+  </si>
+  <si>
+    <t>Imagina trabajar sin ninguna reunión.</t>
+  </si>
+  <si>
+    <t>She offered to help me.</t>
+  </si>
+  <si>
+    <t>Ella se ofreció a ayudarme.</t>
+  </si>
+  <si>
+    <t>Could you open the window?</t>
+  </si>
+  <si>
+    <t>¿Podrías abrir la ventana?</t>
+  </si>
+  <si>
+    <t>He keeps asking difficult questions.</t>
+  </si>
+  <si>
+    <t>Él sigue haciendo preguntas difíciles.</t>
+  </si>
+  <si>
+    <t>She promised to help us.</t>
+  </si>
+  <si>
+    <t>Ella prometió ayudarnos.</t>
+  </si>
+  <si>
+    <t>He pretended to be busy.</t>
+  </si>
+  <si>
+    <t>Él fingió estar ocupado.</t>
+  </si>
+  <si>
+    <t>Does he know your manager?</t>
+  </si>
+  <si>
+    <t>¿Él conoce a tu gerente?</t>
+  </si>
+  <si>
+    <t>I need to finish this today.</t>
+  </si>
+  <si>
+    <t>Necesito terminar esto hoy.</t>
+  </si>
+  <si>
+    <t>They could arrive before noon.</t>
+  </si>
+  <si>
+    <t>Podrían llegar antes del mediodía.</t>
+  </si>
+  <si>
+    <t>He denied sending that message.</t>
+  </si>
+  <si>
+    <t>Él negó enviar ese mensaje.</t>
+  </si>
+  <si>
+    <t>She may need more time.</t>
+  </si>
+  <si>
+    <t>Puede que necesite más tiempo.</t>
+  </si>
+  <si>
+    <t>She pretended to understand everything.</t>
+  </si>
+  <si>
+    <t>Ella fingió entenderlo todo.</t>
+  </si>
+  <si>
+    <t>I don't mind helping you.</t>
+  </si>
+  <si>
+    <t>No me importa ayudarte.</t>
+  </si>
+  <si>
+    <t>We decided to wait outside.</t>
+  </si>
+  <si>
+    <t>Decidimos esperar afuera.</t>
+  </si>
+  <si>
+    <t>He should check the details.</t>
+  </si>
+  <si>
+    <t>Él debería revisar los detalles.</t>
+  </si>
+  <si>
+    <t>We will finish this soon.</t>
+  </si>
+  <si>
+    <t>Terminaremos esto pronto.</t>
+  </si>
+  <si>
+    <t>She aims to finish first.</t>
+  </si>
+  <si>
+    <t>Ella aspira a terminar primero.</t>
+  </si>
+  <si>
+    <t>Would you consider moving abroad?</t>
+  </si>
+  <si>
+    <t>¿Considerarías mudarte al extranjero?</t>
+  </si>
+  <si>
+    <t>I will call you tomorrow.</t>
+  </si>
+  <si>
+    <t>Te llamaré mañana.</t>
+  </si>
+  <si>
+    <t>They intend to expand soon.</t>
+  </si>
+  <si>
+    <t>Pretenden expandirse pronto.</t>
+  </si>
+  <si>
+    <t>She enjoys cooking for friends.</t>
+  </si>
+  <si>
+    <t>Ella disfruta cocinar para amigos.</t>
+  </si>
+  <si>
+    <t>She wants to change jobs.</t>
+  </si>
+  <si>
+    <t>Ella quiere cambiar de trabajo.</t>
+  </si>
+  <si>
+    <t>It may change next week.</t>
+  </si>
+  <si>
+    <t>Puede que cambie la próxima semana.</t>
+  </si>
+  <si>
+    <t>She appreciated receiving your message.</t>
+  </si>
+  <si>
+    <t>Ella agradeció recibir tu mensaje.</t>
+  </si>
+  <si>
+    <t>We managed to solve everything.</t>
+  </si>
+  <si>
+    <t>Logramos resolverlo todo.</t>
+  </si>
+  <si>
+    <t>He might call tonight.</t>
+  </si>
+  <si>
+    <t>Puede que llame esta noche.</t>
+  </si>
+  <si>
+    <t>She resisted answering immediately.</t>
+  </si>
+  <si>
+    <t>Ella se resistió a responder inmediatamente.</t>
+  </si>
+  <si>
+    <t>We aim to improve quality.</t>
+  </si>
+  <si>
+    <t>Buscamos mejorar la calidad.</t>
+  </si>
+  <si>
+    <t>Do you understand the question?</t>
+  </si>
+  <si>
+    <t>¿Entiendes la pregunta?</t>
+  </si>
+  <si>
+    <t>I can't tolerate waiting forever.</t>
+  </si>
+  <si>
+    <t>No tolero esperar para siempre.</t>
+  </si>
+  <si>
+    <t>Would you help me tomorrow?</t>
+  </si>
+  <si>
+    <t>¿Me ayudarías mañana?</t>
+  </si>
+  <si>
+    <t>She learned to speak Dutch.</t>
+  </si>
+  <si>
+    <t>Ella aprendió a hablar neerlandés.</t>
+  </si>
+  <si>
+    <t>We might move next year.</t>
+  </si>
+  <si>
+    <t>Podríamos mudarnos el próximo año.</t>
+  </si>
+  <si>
+    <t>She chose to stay home.</t>
+  </si>
+  <si>
+    <t>Ella eligió quedarse en casa.</t>
+  </si>
+  <si>
+    <t>They denied stealing the money.</t>
+  </si>
+  <si>
+    <t>Negaron robar el dinero.</t>
+  </si>
+  <si>
+    <t>Should we wait outside?</t>
+  </si>
+  <si>
+    <t>¿Deberíamos esperar afuera?</t>
+  </si>
+  <si>
+    <t>I plan to call tomorrow.</t>
+  </si>
+  <si>
+    <t>Planeo llamar mañana.</t>
+  </si>
+  <si>
+    <t>May I ask a question?</t>
+  </si>
+  <si>
+    <t>¿Puedo hacer una pregunta?</t>
+  </si>
+  <si>
+    <t>I hope to see you soon.</t>
+  </si>
+  <si>
+    <t>Espero verte pronto.</t>
+  </si>
+  <si>
+    <t>They will send the documents.</t>
+  </si>
+  <si>
+    <t>Enviarán los documentos.</t>
+  </si>
+  <si>
+    <t>I agreed to meet tomorrow.</t>
+  </si>
+  <si>
+    <t>Acepté reunirnos mañana.</t>
+  </si>
+  <si>
+    <t>I learned to drive safely.</t>
+  </si>
+  <si>
+    <t>Aprendí a conducir con seguridad.</t>
+  </si>
+  <si>
+    <t>Did you finish the report?</t>
+  </si>
+  <si>
+    <t>¿Terminaste el informe?</t>
+  </si>
+  <si>
+    <t>She finished cleaning the kitchen.</t>
+  </si>
+  <si>
+    <t>Ella terminó de limpiar la cocina.</t>
+  </si>
+  <si>
+    <t>They expect to arrive early.</t>
+  </si>
+  <si>
+    <t>Esperan llegar temprano.</t>
+  </si>
+  <si>
+    <t>We could try another option.</t>
+  </si>
+  <si>
+    <t>Podríamos probar otra opción.</t>
+  </si>
+  <si>
+    <t>I resisted buying another phone.</t>
+  </si>
+  <si>
+    <t>Me resistí a comprar otro teléfono.</t>
+  </si>
+  <si>
+    <t>We can meet after work.</t>
+  </si>
+  <si>
+    <t>Podemos reunirnos después del trabajo.</t>
+  </si>
+  <si>
+    <t>We failed to find it.</t>
+  </si>
+  <si>
+    <t>No logramos encontrarlo.</t>
+  </si>
+  <si>
+    <t>This job involves travelling often.</t>
+  </si>
+  <si>
+    <t>Este trabajo implica viajar frecuentemente.</t>
+  </si>
+  <si>
+    <t>Do they work on Fridays?</t>
+  </si>
+  <si>
+    <t>¿Trabajan los viernes?</t>
+  </si>
+  <si>
+    <t>He prepared to answer questions.</t>
+  </si>
+  <si>
+    <t>Él se preparó para responder preguntas.</t>
+  </si>
+  <si>
+    <t>Los médicos recomiendan ejercitarse regularmente.</t>
+  </si>
+  <si>
+    <t>You should talk to her.</t>
+  </si>
+  <si>
+    <t>Deberías hablar con ella.</t>
+  </si>
+  <si>
+    <t>We chose to take the train.</t>
+  </si>
+  <si>
+    <t>Elegimos tomar el tren.</t>
+  </si>
+  <si>
+    <t>They may arrive late.</t>
+  </si>
+  <si>
+    <t>Puede que lleguen tarde.</t>
+  </si>
+  <si>
+    <t>He failed to understand me.</t>
+  </si>
+  <si>
+    <t>Él no logró entenderme.</t>
+  </si>
+  <si>
+    <t>He tolerates working under pressure.</t>
+  </si>
+  <si>
+    <t>Él tolera trabajar bajo presión.</t>
+  </si>
+  <si>
+    <t>He managed to arrive early.</t>
+  </si>
+  <si>
+    <t>Él logró llegar temprano.</t>
+  </si>
+  <si>
+    <t>I practise speaking English daily.</t>
+  </si>
+  <si>
+    <t>Practico hablar inglés diariamente.</t>
+  </si>
+  <si>
+    <t>She would accept that offer.</t>
+  </si>
+  <si>
+    <t>Ella aceptaría esa oferta.</t>
+  </si>
+  <si>
+    <t>They plan to move abroad.</t>
+  </si>
+  <si>
+    <t>Planean mudarse al extranjero.</t>
+  </si>
+  <si>
+    <t>We postponed making the decision.</t>
+  </si>
+  <si>
+    <t>Pospusimos tomar la decisión.</t>
+  </si>
+  <si>
+    <t>Can you help me now?</t>
+  </si>
+  <si>
+    <t>¿Puedes ayudarme ahora?</t>
+  </si>
+  <si>
+    <t>I promise to call tonight.</t>
+  </si>
+  <si>
+    <t>Prometo llamar esta noche.</t>
+  </si>
+  <si>
+    <t>I could call you later.</t>
+  </si>
+  <si>
+    <t>Podría llamarte después.</t>
+  </si>
+  <si>
+    <t>She admitted copying the document.</t>
+  </si>
+  <si>
+    <t>Ella admitió copiar el documento.</t>
+  </si>
+  <si>
+    <t>She must follow the rules.</t>
+  </si>
+  <si>
+    <t>Ella debe seguir las reglas.</t>
+  </si>
+  <si>
+    <t>He refused to answer me.</t>
+  </si>
+  <si>
+    <t>Él se negó a responderme.</t>
+  </si>
+  <si>
+    <t>She can speak three languages.</t>
+  </si>
+  <si>
+    <t>Ella puede hablar tres idiomas.</t>
+  </si>
+  <si>
+    <t>I want to learn English.</t>
+  </si>
+  <si>
+    <t>Quiero aprender inglés.</t>
+  </si>
+  <si>
+    <t>He quit working there yesterday.</t>
+  </si>
+  <si>
+    <t>Él dejó de trabajar allí ayer.</t>
+  </si>
+  <si>
+    <t>I offered to pay today.</t>
+  </si>
+  <si>
+    <t>Me ofrecí a pagar hoy.</t>
+  </si>
+  <si>
+    <t>I can finish this today.</t>
+  </si>
+  <si>
+    <t>Puedo terminar esto hoy.</t>
+  </si>
+  <si>
+    <t>I expect to finish tomorrow.</t>
+  </si>
+  <si>
+    <t>Espero terminar mañana.</t>
+  </si>
+  <si>
+    <t>He avoids driving at night.</t>
+  </si>
+  <si>
+    <t>Él evita conducir de noche.</t>
+  </si>
+  <si>
+    <t>I would choose the cheaper option.</t>
+  </si>
+  <si>
+    <t>Elegiría la opción más barata.</t>
   </si>
 </sst>
 </file>
@@ -2589,485 +3243,965 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="3"/>
-      <c r="B192" s="3"/>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="3"/>
-      <c r="B194" s="3"/>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="3"/>
-      <c r="B195" s="3"/>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="3"/>
-      <c r="B196" s="3"/>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="3"/>
-      <c r="B197" s="3"/>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="3"/>
-      <c r="B202" s="3"/>
-    </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="3"/>
-      <c r="B203" s="3"/>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="3"/>
-      <c r="B204" s="3"/>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="3"/>
-      <c r="B205" s="3"/>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="A206" s="3"/>
-      <c r="B206" s="3"/>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="3"/>
-      <c r="B207" s="3"/>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="3"/>
-      <c r="B208" s="3"/>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="3"/>
-      <c r="B209" s="3"/>
-    </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="3"/>
-      <c r="B210" s="3"/>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="3"/>
-      <c r="B211" s="3"/>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="3"/>
-      <c r="B212" s="3"/>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="3"/>
-      <c r="B213" s="3"/>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="3"/>
-      <c r="B214" s="3"/>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="3"/>
-      <c r="B215" s="3"/>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="3"/>
-      <c r="B216" s="3"/>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="3"/>
-      <c r="B217" s="3"/>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="3"/>
-      <c r="B218" s="3"/>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="3"/>
-      <c r="B220" s="3"/>
-    </row>
-    <row r="221" spans="1:2">
-      <c r="A221" s="3"/>
-      <c r="B221" s="3"/>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="3"/>
-      <c r="B222" s="3"/>
-    </row>
-    <row r="223" spans="1:2">
-      <c r="A223" s="3"/>
-      <c r="B223" s="3"/>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="3"/>
-      <c r="B224" s="3"/>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="3"/>
-      <c r="B225" s="3"/>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" s="3"/>
-      <c r="B226" s="3"/>
-    </row>
-    <row r="227" spans="1:2">
-      <c r="A227" s="3"/>
-      <c r="B227" s="3"/>
-    </row>
-    <row r="228" spans="1:2">
-      <c r="A228" s="3"/>
-      <c r="B228" s="3"/>
-    </row>
-    <row r="229" spans="1:2">
-      <c r="A229" s="3"/>
-      <c r="B229" s="3"/>
-    </row>
-    <row r="230" spans="1:2">
-      <c r="A230" s="3"/>
-      <c r="B230" s="3"/>
-    </row>
-    <row r="231" spans="1:2">
-      <c r="A231" s="3"/>
-      <c r="B231" s="3"/>
-    </row>
-    <row r="232" spans="1:2">
-      <c r="A232" s="3"/>
-      <c r="B232" s="3"/>
-    </row>
-    <row r="233" spans="1:2">
-      <c r="A233" s="3"/>
-      <c r="B233" s="3"/>
-    </row>
-    <row r="234" spans="1:2">
-      <c r="A234" s="3"/>
-      <c r="B234" s="3"/>
-    </row>
-    <row r="235" spans="1:2">
-      <c r="A235" s="3"/>
-      <c r="B235" s="3"/>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="A236" s="3"/>
-      <c r="B236" s="3"/>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" s="3"/>
-      <c r="B237" s="3"/>
-    </row>
-    <row r="238" spans="1:2">
-      <c r="A238" s="3"/>
-      <c r="B238" s="3"/>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" s="3"/>
-      <c r="B239" s="3"/>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="A240" s="3"/>
-      <c r="B240" s="3"/>
-    </row>
-    <row r="241" spans="1:2">
-      <c r="A241" s="3"/>
-      <c r="B241" s="3"/>
-    </row>
-    <row r="242" spans="1:2">
-      <c r="A242" s="3"/>
-      <c r="B242" s="3"/>
-    </row>
-    <row r="243" spans="1:2">
-      <c r="A243" s="3"/>
-      <c r="B243" s="3"/>
-    </row>
-    <row r="244" spans="1:2">
-      <c r="A244" s="3"/>
-      <c r="B244" s="3"/>
-    </row>
-    <row r="245" spans="1:2">
-      <c r="A245" s="3"/>
-      <c r="B245" s="3"/>
-    </row>
-    <row r="246" spans="1:2">
-      <c r="A246" s="3"/>
-      <c r="B246" s="3"/>
-    </row>
-    <row r="247" spans="1:2">
-      <c r="A247" s="3"/>
-      <c r="B247" s="3"/>
-    </row>
-    <row r="248" spans="1:2">
-      <c r="A248" s="3"/>
-      <c r="B248" s="3"/>
-    </row>
-    <row r="249" spans="1:2">
-      <c r="A249" s="3"/>
-      <c r="B249" s="3"/>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="A250" s="3"/>
-      <c r="B250" s="3"/>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="A251" s="3"/>
-      <c r="B251" s="3"/>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="A252" s="3"/>
-      <c r="B252" s="3"/>
-    </row>
-    <row r="253" spans="1:2">
-      <c r="A253" s="3"/>
-      <c r="B253" s="3"/>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="A254" s="3"/>
-      <c r="B254" s="3"/>
-    </row>
-    <row r="255" spans="1:2">
-      <c r="A255" s="3"/>
-      <c r="B255" s="3"/>
-    </row>
-    <row r="256" spans="1:2">
-      <c r="A256" s="3"/>
-      <c r="B256" s="3"/>
-    </row>
-    <row r="257" spans="1:2">
-      <c r="A257" s="3"/>
-      <c r="B257" s="3"/>
-    </row>
-    <row r="258" spans="1:2">
-      <c r="A258" s="3"/>
-      <c r="B258" s="3"/>
-    </row>
-    <row r="259" spans="1:2">
-      <c r="A259" s="3"/>
-      <c r="B259" s="3"/>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="A260" s="3"/>
-      <c r="B260" s="3"/>
-    </row>
-    <row r="261" spans="1:2">
-      <c r="A261" s="3"/>
-      <c r="B261" s="3"/>
-    </row>
-    <row r="262" spans="1:2">
-      <c r="A262" s="3"/>
-      <c r="B262" s="3"/>
-    </row>
-    <row r="263" spans="1:2">
-      <c r="A263" s="3"/>
-      <c r="B263" s="3"/>
-    </row>
-    <row r="264" spans="1:2">
-      <c r="A264" s="3"/>
-      <c r="B264" s="3"/>
-    </row>
-    <row r="265" spans="1:2">
-      <c r="A265" s="3"/>
-      <c r="B265" s="3"/>
-    </row>
-    <row r="266" spans="1:2">
-      <c r="A266" s="3"/>
-      <c r="B266" s="3"/>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267" s="3"/>
-      <c r="B267" s="3"/>
-    </row>
-    <row r="268" spans="1:2">
-      <c r="A268" s="3"/>
-      <c r="B268" s="3"/>
-    </row>
-    <row r="269" spans="1:2">
-      <c r="A269" s="3"/>
-      <c r="B269" s="3"/>
-    </row>
-    <row r="270" spans="1:2">
-      <c r="A270" s="3"/>
-      <c r="B270" s="3"/>
-    </row>
-    <row r="271" spans="1:2">
-      <c r="A271" s="3"/>
-      <c r="B271" s="3"/>
-    </row>
-    <row r="272" spans="1:2">
-      <c r="A272" s="3"/>
-      <c r="B272" s="3"/>
-    </row>
-    <row r="273" spans="1:2">
-      <c r="A273" s="3"/>
-      <c r="B273" s="3"/>
-    </row>
-    <row r="274" spans="1:2">
-      <c r="A274" s="3"/>
-      <c r="B274" s="3"/>
-    </row>
-    <row r="275" spans="1:2">
-      <c r="A275" s="3"/>
-      <c r="B275" s="3"/>
-    </row>
-    <row r="276" spans="1:2">
-      <c r="A276" s="3"/>
-      <c r="B276" s="3"/>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="A277" s="3"/>
-      <c r="B277" s="3"/>
-    </row>
-    <row r="278" spans="1:2">
-      <c r="A278" s="3"/>
-      <c r="B278" s="3"/>
-    </row>
-    <row r="279" spans="1:2">
-      <c r="A279" s="3"/>
-      <c r="B279" s="3"/>
-    </row>
-    <row r="280" spans="1:2">
-      <c r="A280" s="3"/>
-      <c r="B280" s="3"/>
-    </row>
-    <row r="281" spans="1:2">
-      <c r="A281" s="3"/>
-      <c r="B281" s="3"/>
-    </row>
-    <row r="282" spans="1:2">
-      <c r="A282" s="3"/>
-      <c r="B282" s="3"/>
-    </row>
-    <row r="283" spans="1:2">
-      <c r="A283" s="3"/>
-      <c r="B283" s="3"/>
-    </row>
-    <row r="284" spans="1:2">
-      <c r="A284" s="3"/>
-      <c r="B284" s="3"/>
-    </row>
-    <row r="285" spans="1:2">
-      <c r="A285" s="3"/>
-      <c r="B285" s="3"/>
-    </row>
-    <row r="286" spans="1:2">
-      <c r="A286" s="3"/>
-      <c r="B286" s="3"/>
-    </row>
-    <row r="287" spans="1:2">
-      <c r="A287" s="3"/>
-      <c r="B287" s="3"/>
-    </row>
-    <row r="288" spans="1:2">
-      <c r="A288" s="3"/>
-      <c r="B288" s="3"/>
+    <row r="169" spans="1:2" ht="16">
+      <c r="A169" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="16">
+      <c r="A170" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="16">
+      <c r="A171" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="16">
+      <c r="A172" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="16">
+      <c r="A173" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="16">
+      <c r="A174" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="16">
+      <c r="A175" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="16">
+      <c r="A176" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="16">
+      <c r="A177" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="16">
+      <c r="A178" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="16">
+      <c r="A179" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="16">
+      <c r="A180" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="16">
+      <c r="A181" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="16">
+      <c r="A182" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="16">
+      <c r="A183" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="16">
+      <c r="A184" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="16">
+      <c r="A185" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="16">
+      <c r="A186" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="16">
+      <c r="A187" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="16">
+      <c r="A188" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="16">
+      <c r="A189" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="16">
+      <c r="A190" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="16">
+      <c r="A191" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="16">
+      <c r="A192" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="16">
+      <c r="A193" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="16">
+      <c r="A194" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="16">
+      <c r="A195" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="16">
+      <c r="A196" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="16">
+      <c r="A197" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="16">
+      <c r="A198" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="16">
+      <c r="A199" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="16">
+      <c r="A200" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="16">
+      <c r="A201" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="16">
+      <c r="A202" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="16">
+      <c r="A203" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="16">
+      <c r="A204" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="16">
+      <c r="A205" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="16">
+      <c r="A206" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="16">
+      <c r="A207" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="16">
+      <c r="A208" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="16">
+      <c r="A209" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="16">
+      <c r="A210" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="16">
+      <c r="A211" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="16">
+      <c r="A212" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="16">
+      <c r="A213" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="16">
+      <c r="A214" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="16">
+      <c r="A215" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="16">
+      <c r="A216" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="16">
+      <c r="A217" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="16">
+      <c r="A218" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="16">
+      <c r="A219" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="16">
+      <c r="A220" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="16">
+      <c r="A221" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="16">
+      <c r="A222" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="16">
+      <c r="A223" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="16">
+      <c r="A224" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="16">
+      <c r="A225" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="16">
+      <c r="A226" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="16">
+      <c r="A227" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="16">
+      <c r="A228" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="16">
+      <c r="A229" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="16">
+      <c r="A230" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="16">
+      <c r="A231" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="16">
+      <c r="A232" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="16">
+      <c r="A233" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="16">
+      <c r="A234" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="16">
+      <c r="A235" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="16">
+      <c r="A236" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="16">
+      <c r="A237" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="16">
+      <c r="A238" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="16">
+      <c r="A239" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="16">
+      <c r="A240" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="16">
+      <c r="A241" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="16">
+      <c r="A242" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="16">
+      <c r="A243" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="16">
+      <c r="A244" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="16">
+      <c r="A245" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="16">
+      <c r="A246" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="16">
+      <c r="A247" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="16">
+      <c r="A248" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="16">
+      <c r="A249" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="16">
+      <c r="A250" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="16">
+      <c r="A251" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="16">
+      <c r="A252" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="16">
+      <c r="A253" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" ht="16">
+      <c r="A254" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" ht="16">
+      <c r="A255" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" ht="16">
+      <c r="A256" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" ht="16">
+      <c r="A257" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" ht="16">
+      <c r="A258" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="16">
+      <c r="A259" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" ht="16">
+      <c r="A260" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" ht="16">
+      <c r="A261" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" ht="32">
+      <c r="A262" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" ht="16">
+      <c r="A263" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" ht="16">
+      <c r="A264" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="16">
+      <c r="A265" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="16">
+      <c r="A266" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="16">
+      <c r="A267" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="16">
+      <c r="A268" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="16">
+      <c r="A269" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="16">
+      <c r="A270" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="16">
+      <c r="A271" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="16">
+      <c r="A272" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="16">
+      <c r="A273" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="16">
+      <c r="A274" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="16">
+      <c r="A275" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="16">
+      <c r="A276" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" ht="16">
+      <c r="A277" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" ht="16">
+      <c r="A278" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" ht="16">
+      <c r="A279" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" ht="16">
+      <c r="A280" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" ht="16">
+      <c r="A281" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" ht="16">
+      <c r="A282" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" ht="16">
+      <c r="A283" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="16">
+      <c r="A284" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="16">
+      <c r="A285" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" ht="16">
+      <c r="A286" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" ht="16">
+      <c r="A287" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" ht="16">
+      <c r="A288" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="3"/>

--- a/tts/voices.xlsx
+++ b/tts/voices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joelcespedes/Desktop/voices/tts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504677C7-7EA1-D848-B29E-9195823376C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3D3AE0-D65B-A64C-8CC8-F47BFEC3699D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="70880" yWindow="8160" windowWidth="31520" windowHeight="35040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="741">
   <si>
     <t>Who looks after your dog?</t>
   </si>
@@ -1673,6 +1673,576 @@
   </si>
   <si>
     <t>Elegiría la opción más barata.</t>
+  </si>
+  <si>
+    <t>I enjoy cooking at home.</t>
+  </si>
+  <si>
+    <t>She decided to change jobs.</t>
+  </si>
+  <si>
+    <t>We finished cleaning the kitchen.</t>
+  </si>
+  <si>
+    <t>They agreed to meet tomorrow.</t>
+  </si>
+  <si>
+    <t>She keeps asking the same question.</t>
+  </si>
+  <si>
+    <t>He promised to call me tonight.</t>
+  </si>
+  <si>
+    <t>I don't mind waiting here.</t>
+  </si>
+  <si>
+    <t>We considered moving to another city.</t>
+  </si>
+  <si>
+    <t>She hopes to find a better apartment.</t>
+  </si>
+  <si>
+    <t>He suggested taking a taxi.</t>
+  </si>
+  <si>
+    <t>I love spending time with my family.</t>
+  </si>
+  <si>
+    <t>She refused to answer the question.</t>
+  </si>
+  <si>
+    <t>We discussed buying a new car.</t>
+  </si>
+  <si>
+    <t>He admitted making a mistake.</t>
+  </si>
+  <si>
+    <t>I plan to travel next month.</t>
+  </si>
+  <si>
+    <t>She practices speaking English every day.</t>
+  </si>
+  <si>
+    <t>He quit smoking last year.</t>
+  </si>
+  <si>
+    <t>We expect to arrive before eight.</t>
+  </si>
+  <si>
+    <t>I recommend trying this restaurant.</t>
+  </si>
+  <si>
+    <t>She enjoys listening to music.</t>
+  </si>
+  <si>
+    <t>He offered to help me.</t>
+  </si>
+  <si>
+    <t>They avoided talking about the problem.</t>
+  </si>
+  <si>
+    <t>I finished writing the email.</t>
+  </si>
+  <si>
+    <t>She chose to stay at home.</t>
+  </si>
+  <si>
+    <t>He keeps forgetting his keys.</t>
+  </si>
+  <si>
+    <t>We enjoy walking after dinner.</t>
+  </si>
+  <si>
+    <t>They managed to solve the problem.</t>
+  </si>
+  <si>
+    <t>I can't imagine living there.</t>
+  </si>
+  <si>
+    <t>She mentioned seeing him yesterday.</t>
+  </si>
+  <si>
+    <t>He learned to cook when he was young.</t>
+  </si>
+  <si>
+    <t>We postponed leaving until Monday.</t>
+  </si>
+  <si>
+    <t>I avoid eating too late.</t>
+  </si>
+  <si>
+    <t>She intends to start a business.</t>
+  </si>
+  <si>
+    <t>He enjoys working from home.</t>
+  </si>
+  <si>
+    <t>They denied taking the money.</t>
+  </si>
+  <si>
+    <t>I can't afford to wait any longer.</t>
+  </si>
+  <si>
+    <t>She suggested going by train.</t>
+  </si>
+  <si>
+    <t>We finished watching the movie.</t>
+  </si>
+  <si>
+    <t>He deserves to know the truth.</t>
+  </si>
+  <si>
+    <t>She avoids using her phone at work.</t>
+  </si>
+  <si>
+    <t>They decided to sell the house.</t>
+  </si>
+  <si>
+    <t>He admitted lying to his boss.</t>
+  </si>
+  <si>
+    <t>I enjoy learning new things.</t>
+  </si>
+  <si>
+    <t>She failed to finish the project.</t>
+  </si>
+  <si>
+    <t>We considered staying another night.</t>
+  </si>
+  <si>
+    <t>He doesn't mind working on Saturdays.</t>
+  </si>
+  <si>
+    <t>She stopped complaining about everything.</t>
+  </si>
+  <si>
+    <t>We discussed changing the schedule.</t>
+  </si>
+  <si>
+    <t>He pretended to understand me.</t>
+  </si>
+  <si>
+    <t>I miss talking to my old friends.</t>
+  </si>
+  <si>
+    <t>She recommended visiting the museum.</t>
+  </si>
+  <si>
+    <t>They arranged to meet at the station.</t>
+  </si>
+  <si>
+    <t>He keeps checking his phone.</t>
+  </si>
+  <si>
+    <t>I enjoy waking up early.</t>
+  </si>
+  <si>
+    <t>She promised to be careful.</t>
+  </si>
+  <si>
+    <t>We avoided spending too much money.</t>
+  </si>
+  <si>
+    <t>He finished repairing the car.</t>
+  </si>
+  <si>
+    <t>I seem to understand it now.</t>
+  </si>
+  <si>
+    <t>She dislikes waiting in long queues.</t>
+  </si>
+  <si>
+    <t>They considered changing their plans.</t>
+  </si>
+  <si>
+    <t>He refused to pay for it.</t>
+  </si>
+  <si>
+    <t>I practice writing in English every morning.</t>
+  </si>
+  <si>
+    <t>She admitted breaking the glass.</t>
+  </si>
+  <si>
+    <t>We expect to hear from them tomorrow.</t>
+  </si>
+  <si>
+    <t>He enjoys playing football with his friends.</t>
+  </si>
+  <si>
+    <t>I avoid drinking coffee at night.</t>
+  </si>
+  <si>
+    <t>She offered to drive us home.</t>
+  </si>
+  <si>
+    <t>We love travelling together.</t>
+  </si>
+  <si>
+    <t>He decided to tell the truth.</t>
+  </si>
+  <si>
+    <t>I decided to take a break.</t>
+  </si>
+  <si>
+    <t>She enjoys dancing at parties.</t>
+  </si>
+  <si>
+    <t>They postponed making a decision.</t>
+  </si>
+  <si>
+    <t>He agreed to wait outside.</t>
+  </si>
+  <si>
+    <t>I can't stand hearing that noise.</t>
+  </si>
+  <si>
+    <t>She keeps changing her mind.</t>
+  </si>
+  <si>
+    <t>We plan to leave early.</t>
+  </si>
+  <si>
+    <t>He enjoys fixing things himself.</t>
+  </si>
+  <si>
+    <t>I considered calling her yesterday.</t>
+  </si>
+  <si>
+    <t>She chose to study abroad.</t>
+  </si>
+  <si>
+    <t>They enjoy eating outside in summer.</t>
+  </si>
+  <si>
+    <t>He avoids talking during meetings.</t>
+  </si>
+  <si>
+    <t>I managed to open the door.</t>
+  </si>
+  <si>
+    <t>She finished reading the book.</t>
+  </si>
+  <si>
+    <t>We miss seeing our friends.</t>
+  </si>
+  <si>
+    <t>He hopes to buy a house one day.</t>
+  </si>
+  <si>
+    <t>I enjoy watching documentaries.</t>
+  </si>
+  <si>
+    <t>She suggested meeting earlier.</t>
+  </si>
+  <si>
+    <t>They refused to leave the building.</t>
+  </si>
+  <si>
+    <t>He practices playing the guitar every day.</t>
+  </si>
+  <si>
+    <t>She intends to learn Spanish.</t>
+  </si>
+  <si>
+    <t>We enjoy talking about movies.</t>
+  </si>
+  <si>
+    <t>She agreed to help us tomorrow.</t>
+  </si>
+  <si>
+    <t>I promised to send the document.</t>
+  </si>
+  <si>
+    <t>She avoids spending time on social media.</t>
+  </si>
+  <si>
+    <t>They finished painting the room.</t>
+  </si>
+  <si>
+    <t>Disfruto cocinar en casa.</t>
+  </si>
+  <si>
+    <t>Ella decidió cambiar de trabajo.</t>
+  </si>
+  <si>
+    <t>Terminamos de limpiar la cocina.</t>
+  </si>
+  <si>
+    <t>Acordaron reunirse mañana.</t>
+  </si>
+  <si>
+    <t>Echo de menos vivir cerca de la playa.</t>
+  </si>
+  <si>
+    <t>Ella sigue haciendo la misma pregunta.</t>
+  </si>
+  <si>
+    <t>Él prometió llamarme esta noche.</t>
+  </si>
+  <si>
+    <t>No me importa esperar aquí.</t>
+  </si>
+  <si>
+    <t>Consideramos mudarnos a otra ciudad.</t>
+  </si>
+  <si>
+    <t>Ella espera encontrar un piso mejor.</t>
+  </si>
+  <si>
+    <t>Él sugirió tomar un taxi.</t>
+  </si>
+  <si>
+    <t>Me encanta pasar tiempo con mi familia.</t>
+  </si>
+  <si>
+    <t>Ella se negó a responder la pregunta.</t>
+  </si>
+  <si>
+    <t>Hablamos de comprar un coche nuevo.</t>
+  </si>
+  <si>
+    <t>Él admitió haber cometido un error.</t>
+  </si>
+  <si>
+    <t>Planeo viajar el mes que viene.</t>
+  </si>
+  <si>
+    <t>Ella practica hablar inglés todos los días.</t>
+  </si>
+  <si>
+    <t>Él dejó de fumar el año pasado.</t>
+  </si>
+  <si>
+    <t>Esperamos llegar antes de las ocho.</t>
+  </si>
+  <si>
+    <t>Recomiendo probar este restaurante.</t>
+  </si>
+  <si>
+    <t>Ella disfruta escuchar música.</t>
+  </si>
+  <si>
+    <t>Él se ofreció a ayudarme.</t>
+  </si>
+  <si>
+    <t>Evitaron hablar del problema.</t>
+  </si>
+  <si>
+    <t>Terminé de escribir el correo.</t>
+  </si>
+  <si>
+    <t>Él sigue olvidando sus llaves.</t>
+  </si>
+  <si>
+    <t>Disfrutamos caminar después de cenar.</t>
+  </si>
+  <si>
+    <t>Lograron resolver el problema.</t>
+  </si>
+  <si>
+    <t>No puedo imaginar vivir allí.</t>
+  </si>
+  <si>
+    <t>Ella mencionó haberlo visto ayer.</t>
+  </si>
+  <si>
+    <t>Él aprendió a cocinar cuando era joven.</t>
+  </si>
+  <si>
+    <t>Aplazamos irnos hasta el lunes.</t>
+  </si>
+  <si>
+    <t>Evito comer demasiado tarde.</t>
+  </si>
+  <si>
+    <t>Ella tiene intención de montar un negocio.</t>
+  </si>
+  <si>
+    <t>Él disfruta trabajar desde casa.</t>
+  </si>
+  <si>
+    <t>Negaron haber cogido el dinero.</t>
+  </si>
+  <si>
+    <t>No puedo permitirme esperar más.</t>
+  </si>
+  <si>
+    <t>Ella sugirió ir en tren.</t>
+  </si>
+  <si>
+    <t>Terminamos de ver la película.</t>
+  </si>
+  <si>
+    <t>Él merece saber la verdad.</t>
+  </si>
+  <si>
+    <t>Ella evita usar el teléfono en el trabajo.</t>
+  </si>
+  <si>
+    <t>Decidieron vender la casa.</t>
+  </si>
+  <si>
+    <t>Él admitió haber mentido a su jefe.</t>
+  </si>
+  <si>
+    <t>Disfruto aprender cosas nuevas.</t>
+  </si>
+  <si>
+    <t>Ella no logró terminar el proyecto.</t>
+  </si>
+  <si>
+    <t>Consideramos quedarnos otra noche.</t>
+  </si>
+  <si>
+    <t>A él no le importa trabajar los sábados.</t>
+  </si>
+  <si>
+    <t>Ella dejó de quejarse de todo.</t>
+  </si>
+  <si>
+    <t>Hablamos de cambiar el horario.</t>
+  </si>
+  <si>
+    <t>Él fingió entenderme.</t>
+  </si>
+  <si>
+    <t>Echo de menos hablar con mis antiguos amigos.</t>
+  </si>
+  <si>
+    <t>Ella recomendó visitar el museo.</t>
+  </si>
+  <si>
+    <t>Quedaron en reunirse en la estación.</t>
+  </si>
+  <si>
+    <t>Él sigue mirando el teléfono.</t>
+  </si>
+  <si>
+    <t>Disfruto despertarme temprano.</t>
+  </si>
+  <si>
+    <t>Ella prometió tener cuidado.</t>
+  </si>
+  <si>
+    <t>Evitamos gastar demasiado dinero.</t>
+  </si>
+  <si>
+    <t>Él terminó de reparar el coche.</t>
+  </si>
+  <si>
+    <t>Parece que ahora lo entiendo.</t>
+  </si>
+  <si>
+    <t>A ella no le gusta esperar en colas largas.</t>
+  </si>
+  <si>
+    <t>Consideraron cambiar sus planes.</t>
+  </si>
+  <si>
+    <t>Él se negó a pagarlo.</t>
+  </si>
+  <si>
+    <t>Practico escribir en inglés cada mañana.</t>
+  </si>
+  <si>
+    <t>Ella admitió haber roto el cristal.</t>
+  </si>
+  <si>
+    <t>Esperamos tener noticias de ellos mañana.</t>
+  </si>
+  <si>
+    <t>Él disfruta jugar al fútbol con sus amigos.</t>
+  </si>
+  <si>
+    <t>Evito beber café por la noche.</t>
+  </si>
+  <si>
+    <t>Ella se ofreció a llevarnos a casa en coche.</t>
+  </si>
+  <si>
+    <t>Nos encanta viajar juntos.</t>
+  </si>
+  <si>
+    <t>Él decidió decir la verdad.</t>
+  </si>
+  <si>
+    <t>Decidí tomarme un descanso.</t>
+  </si>
+  <si>
+    <t>Ella disfruta bailar en las fiestas.</t>
+  </si>
+  <si>
+    <t>Aplazaron tomar una decisión.</t>
+  </si>
+  <si>
+    <t>Él aceptó esperar fuera.</t>
+  </si>
+  <si>
+    <t>No soporto escuchar ese ruido.</t>
+  </si>
+  <si>
+    <t>Ella sigue cambiando de opinión.</t>
+  </si>
+  <si>
+    <t>Planeamos salir temprano.</t>
+  </si>
+  <si>
+    <t>Él disfruta arreglar las cosas él mismo.</t>
+  </si>
+  <si>
+    <t>Consideré llamarla ayer.</t>
+  </si>
+  <si>
+    <t>Ella eligió estudiar en el extranjero.</t>
+  </si>
+  <si>
+    <t>Disfrutan comer fuera en verano.</t>
+  </si>
+  <si>
+    <t>Él evita hablar durante las reuniones.</t>
+  </si>
+  <si>
+    <t>Logré abrir la puerta.</t>
+  </si>
+  <si>
+    <t>Ella terminó de leer el libro.</t>
+  </si>
+  <si>
+    <t>Echamos de menos ver a nuestros amigos.</t>
+  </si>
+  <si>
+    <t>Él espera comprar una casa algún día.</t>
+  </si>
+  <si>
+    <t>Disfruto ver documentales.</t>
+  </si>
+  <si>
+    <t>Ella sugirió reunirnos más temprano.</t>
+  </si>
+  <si>
+    <t>Se negaron a salir del edificio.</t>
+  </si>
+  <si>
+    <t>Él practica tocar la guitarra todos los días.</t>
+  </si>
+  <si>
+    <t>Ella tiene intención de aprender español.</t>
+  </si>
+  <si>
+    <t>Disfrutamos hablar de películas.</t>
+  </si>
+  <si>
+    <t>Ella aceptó ayudarnos mañana.</t>
+  </si>
+  <si>
+    <t>Prometí enviar el documento.</t>
+  </si>
+  <si>
+    <t>Ella evita pasar tiempo en las redes sociales.</t>
+  </si>
+  <si>
+    <t>Terminaron de pintar la habitación.</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +2463,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B652"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -2475,7 +3045,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="16">
+    <row r="73" spans="1:2" ht="15">
       <c r="A73" s="2" t="s">
         <v>143</v>
       </c>
@@ -2483,7 +3053,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="16">
+    <row r="74" spans="1:2" ht="15">
       <c r="A74" s="2" t="s">
         <v>144</v>
       </c>
@@ -2491,7 +3061,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="16">
+    <row r="75" spans="1:2" ht="15">
       <c r="A75" s="2" t="s">
         <v>145</v>
       </c>
@@ -2499,7 +3069,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="16">
+    <row r="76" spans="1:2" ht="15">
       <c r="A76" s="2" t="s">
         <v>146</v>
       </c>
@@ -2507,7 +3077,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="16">
+    <row r="77" spans="1:2" ht="15">
       <c r="A77" s="2" t="s">
         <v>147</v>
       </c>
@@ -2515,7 +3085,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="16">
+    <row r="78" spans="1:2" ht="15">
       <c r="A78" s="2" t="s">
         <v>148</v>
       </c>
@@ -2523,7 +3093,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="16">
+    <row r="79" spans="1:2" ht="15">
       <c r="A79" s="2" t="s">
         <v>149</v>
       </c>
@@ -2531,7 +3101,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="16">
+    <row r="80" spans="1:2" ht="15">
       <c r="A80" s="2" t="s">
         <v>150</v>
       </c>
@@ -2539,7 +3109,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="16">
+    <row r="81" spans="1:2" ht="15">
       <c r="A81" s="2" t="s">
         <v>151</v>
       </c>
@@ -2547,7 +3117,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="16">
+    <row r="82" spans="1:2" ht="15">
       <c r="A82" s="2" t="s">
         <v>152</v>
       </c>
@@ -2555,7 +3125,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="16">
+    <row r="83" spans="1:2" ht="15">
       <c r="A83" s="2" t="s">
         <v>153</v>
       </c>
@@ -2563,7 +3133,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="16">
+    <row r="84" spans="1:2" ht="15">
       <c r="A84" s="2" t="s">
         <v>154</v>
       </c>
@@ -2571,7 +3141,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="16">
+    <row r="85" spans="1:2" ht="15">
       <c r="A85" s="2" t="s">
         <v>155</v>
       </c>
@@ -2579,7 +3149,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="16">
+    <row r="86" spans="1:2" ht="15">
       <c r="A86" s="2" t="s">
         <v>156</v>
       </c>
@@ -2587,7 +3157,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="32">
+    <row r="87" spans="1:2" ht="30">
       <c r="A87" s="2" t="s">
         <v>157</v>
       </c>
@@ -2595,7 +3165,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="16">
+    <row r="88" spans="1:2" ht="15">
       <c r="A88" s="2" t="s">
         <v>158</v>
       </c>
@@ -2603,7 +3173,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="16">
+    <row r="89" spans="1:2" ht="15">
       <c r="A89" s="2" t="s">
         <v>159</v>
       </c>
@@ -2611,7 +3181,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="16">
+    <row r="90" spans="1:2" ht="15">
       <c r="A90" s="2" t="s">
         <v>160</v>
       </c>
@@ -2619,7 +3189,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="16">
+    <row r="91" spans="1:2" ht="15">
       <c r="A91" s="2" t="s">
         <v>161</v>
       </c>
@@ -2627,7 +3197,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="32">
+    <row r="92" spans="1:2" ht="15">
       <c r="A92" s="2" t="s">
         <v>162</v>
       </c>
@@ -2635,7 +3205,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="16">
+    <row r="93" spans="1:2" ht="15">
       <c r="A93" s="2" t="s">
         <v>163</v>
       </c>
@@ -2643,7 +3213,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="16">
+    <row r="94" spans="1:2" ht="15">
       <c r="A94" s="2" t="s">
         <v>164</v>
       </c>
@@ -2651,7 +3221,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="16">
+    <row r="95" spans="1:2" ht="15">
       <c r="A95" s="2" t="s">
         <v>165</v>
       </c>
@@ -2659,7 +3229,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="16">
+    <row r="96" spans="1:2" ht="15">
       <c r="A96" s="2" t="s">
         <v>166</v>
       </c>
@@ -2667,7 +3237,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="16">
+    <row r="97" spans="1:2" ht="15">
       <c r="A97" s="2" t="s">
         <v>167</v>
       </c>
@@ -2675,7 +3245,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="16">
+    <row r="98" spans="1:2" ht="15">
       <c r="A98" s="2" t="s">
         <v>168</v>
       </c>
@@ -2683,7 +3253,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="16">
+    <row r="99" spans="1:2" ht="15">
       <c r="A99" s="2" t="s">
         <v>169</v>
       </c>
@@ -2691,7 +3261,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="16">
+    <row r="100" spans="1:2" ht="15">
       <c r="A100" s="2" t="s">
         <v>170</v>
       </c>
@@ -2699,7 +3269,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="16">
+    <row r="101" spans="1:2" ht="15">
       <c r="A101" s="2" t="s">
         <v>171</v>
       </c>
@@ -2707,7 +3277,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="16">
+    <row r="102" spans="1:2" ht="15">
       <c r="A102" s="2" t="s">
         <v>172</v>
       </c>
@@ -2715,7 +3285,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="16">
+    <row r="103" spans="1:2" ht="15">
       <c r="A103" s="2" t="s">
         <v>173</v>
       </c>
@@ -2723,7 +3293,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="16">
+    <row r="104" spans="1:2" ht="15">
       <c r="A104" s="2" t="s">
         <v>174</v>
       </c>
@@ -2731,7 +3301,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="16">
+    <row r="105" spans="1:2" ht="15">
       <c r="A105" s="2" t="s">
         <v>175</v>
       </c>
@@ -2739,7 +3309,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="16">
+    <row r="106" spans="1:2" ht="15">
       <c r="A106" s="2" t="s">
         <v>176</v>
       </c>
@@ -2747,7 +3317,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="16">
+    <row r="107" spans="1:2" ht="15">
       <c r="A107" s="2" t="s">
         <v>177</v>
       </c>
@@ -2755,7 +3325,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="16">
+    <row r="108" spans="1:2" ht="15">
       <c r="A108" s="2" t="s">
         <v>178</v>
       </c>
@@ -2763,7 +3333,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="16">
+    <row r="109" spans="1:2" ht="15">
       <c r="A109" s="2" t="s">
         <v>179</v>
       </c>
@@ -2771,7 +3341,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16">
+    <row r="110" spans="1:2" ht="15">
       <c r="A110" s="2" t="s">
         <v>180</v>
       </c>
@@ -2779,7 +3349,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="16">
+    <row r="111" spans="1:2" ht="15">
       <c r="A111" s="2" t="s">
         <v>181</v>
       </c>
@@ -2787,7 +3357,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="16">
+    <row r="112" spans="1:2" ht="15">
       <c r="A112" s="2" t="s">
         <v>182</v>
       </c>
@@ -2795,7 +3365,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16">
+    <row r="113" spans="1:2" ht="15">
       <c r="A113" s="2" t="s">
         <v>183</v>
       </c>
@@ -2803,7 +3373,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16">
+    <row r="114" spans="1:2" ht="15">
       <c r="A114" s="2" t="s">
         <v>184</v>
       </c>
@@ -2811,7 +3381,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16">
+    <row r="115" spans="1:2" ht="15">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -2819,7 +3389,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="16">
+    <row r="116" spans="1:2" ht="15">
       <c r="A116" s="2" t="s">
         <v>186</v>
       </c>
@@ -2827,7 +3397,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="16">
+    <row r="117" spans="1:2" ht="15">
       <c r="A117" s="2" t="s">
         <v>187</v>
       </c>
@@ -2835,7 +3405,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="16">
+    <row r="118" spans="1:2" ht="15">
       <c r="A118" s="2" t="s">
         <v>188</v>
       </c>
@@ -2843,7 +3413,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="16">
+    <row r="119" spans="1:2" ht="15">
       <c r="A119" s="2" t="s">
         <v>189</v>
       </c>
@@ -2851,7 +3421,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="16">
+    <row r="120" spans="1:2" ht="15">
       <c r="A120" s="2" t="s">
         <v>190</v>
       </c>
@@ -2859,7 +3429,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="16">
+    <row r="121" spans="1:2" ht="15">
       <c r="A121" s="2" t="s">
         <v>191</v>
       </c>
@@ -2867,7 +3437,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="16">
+    <row r="122" spans="1:2" ht="15">
       <c r="A122" s="2" t="s">
         <v>192</v>
       </c>
@@ -2875,7 +3445,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="16">
+    <row r="123" spans="1:2" ht="15">
       <c r="A123" s="2" t="s">
         <v>193</v>
       </c>
@@ -2883,7 +3453,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="16">
+    <row r="124" spans="1:2" ht="15">
       <c r="A124" s="2" t="s">
         <v>194</v>
       </c>
@@ -2891,7 +3461,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="16">
+    <row r="125" spans="1:2" ht="15">
       <c r="A125" s="2" t="s">
         <v>195</v>
       </c>
@@ -2899,7 +3469,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="16">
+    <row r="126" spans="1:2" ht="15">
       <c r="A126" s="2" t="s">
         <v>196</v>
       </c>
@@ -2907,7 +3477,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="16">
+    <row r="127" spans="1:2" ht="15">
       <c r="A127" s="2" t="s">
         <v>197</v>
       </c>
@@ -2915,7 +3485,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="16">
+    <row r="128" spans="1:2" ht="15">
       <c r="A128" s="2" t="s">
         <v>198</v>
       </c>
@@ -2923,7 +3493,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="16">
+    <row r="129" spans="1:2" ht="15">
       <c r="A129" s="2" t="s">
         <v>199</v>
       </c>
@@ -2931,7 +3501,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="16">
+    <row r="130" spans="1:2" ht="15">
       <c r="A130" s="2" t="s">
         <v>200</v>
       </c>
@@ -2939,7 +3509,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="16">
+    <row r="131" spans="1:2" ht="15">
       <c r="A131" s="2" t="s">
         <v>201</v>
       </c>
@@ -2947,7 +3517,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="16">
+    <row r="132" spans="1:2" ht="15">
       <c r="A132" s="2" t="s">
         <v>202</v>
       </c>
@@ -2955,7 +3525,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="16">
+    <row r="133" spans="1:2" ht="15">
       <c r="A133" s="2" t="s">
         <v>203</v>
       </c>
@@ -2963,7 +3533,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="16">
+    <row r="134" spans="1:2" ht="15">
       <c r="A134" s="2" t="s">
         <v>204</v>
       </c>
@@ -2971,7 +3541,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="16">
+    <row r="135" spans="1:2" ht="15">
       <c r="A135" s="2" t="s">
         <v>205</v>
       </c>
@@ -2979,7 +3549,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="16">
+    <row r="136" spans="1:2" ht="15">
       <c r="A136" s="2" t="s">
         <v>206</v>
       </c>
@@ -2987,7 +3557,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="16">
+    <row r="137" spans="1:2" ht="15">
       <c r="A137" s="2" t="s">
         <v>207</v>
       </c>
@@ -2995,7 +3565,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="16">
+    <row r="138" spans="1:2" ht="15">
       <c r="A138" s="2" t="s">
         <v>208</v>
       </c>
@@ -3003,7 +3573,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="16">
+    <row r="139" spans="1:2" ht="15">
       <c r="A139" s="2" t="s">
         <v>209</v>
       </c>
@@ -3011,7 +3581,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="16">
+    <row r="140" spans="1:2" ht="15">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
@@ -3019,7 +3589,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="16">
+    <row r="141" spans="1:2" ht="15">
       <c r="A141" s="2" t="s">
         <v>211</v>
       </c>
@@ -3027,7 +3597,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="16">
+    <row r="142" spans="1:2" ht="15">
       <c r="A142" s="2" t="s">
         <v>212</v>
       </c>
@@ -3035,7 +3605,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="16">
+    <row r="143" spans="1:2" ht="15">
       <c r="A143" s="2" t="s">
         <v>213</v>
       </c>
@@ -3043,7 +3613,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="16">
+    <row r="144" spans="1:2" ht="15">
       <c r="A144" s="2" t="s">
         <v>214</v>
       </c>
@@ -3051,7 +3621,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="16">
+    <row r="145" spans="1:2" ht="15">
       <c r="A145" s="2" t="s">
         <v>215</v>
       </c>
@@ -3059,7 +3629,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="16">
+    <row r="146" spans="1:2" ht="15">
       <c r="A146" s="2" t="s">
         <v>216</v>
       </c>
@@ -3067,7 +3637,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="16">
+    <row r="147" spans="1:2" ht="15">
       <c r="A147" s="2" t="s">
         <v>217</v>
       </c>
@@ -3075,7 +3645,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="16">
+    <row r="148" spans="1:2" ht="15">
       <c r="A148" s="2" t="s">
         <v>218</v>
       </c>
@@ -3083,7 +3653,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="16">
+    <row r="149" spans="1:2" ht="15">
       <c r="A149" s="2" t="s">
         <v>219</v>
       </c>
@@ -3091,7 +3661,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="16">
+    <row r="150" spans="1:2" ht="15">
       <c r="A150" s="2" t="s">
         <v>220</v>
       </c>
@@ -3099,7 +3669,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="16">
+    <row r="151" spans="1:2" ht="15">
       <c r="A151" s="2" t="s">
         <v>221</v>
       </c>
@@ -3107,7 +3677,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="16">
+    <row r="152" spans="1:2" ht="15">
       <c r="A152" s="2" t="s">
         <v>222</v>
       </c>
@@ -3115,7 +3685,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="16">
+    <row r="153" spans="1:2" ht="15">
       <c r="A153" s="2" t="s">
         <v>303</v>
       </c>
@@ -3123,7 +3693,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="16">
+    <row r="154" spans="1:2" ht="15">
       <c r="A154" s="2" t="s">
         <v>304</v>
       </c>
@@ -3131,7 +3701,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="16">
+    <row r="155" spans="1:2" ht="15">
       <c r="A155" s="2" t="s">
         <v>305</v>
       </c>
@@ -3139,7 +3709,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="16">
+    <row r="156" spans="1:2" ht="15">
       <c r="A156" s="2" t="s">
         <v>306</v>
       </c>
@@ -3147,7 +3717,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="16">
+    <row r="157" spans="1:2" ht="15">
       <c r="A157" s="2" t="s">
         <v>307</v>
       </c>
@@ -3155,7 +3725,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="16">
+    <row r="158" spans="1:2" ht="15">
       <c r="A158" s="2" t="s">
         <v>308</v>
       </c>
@@ -3163,7 +3733,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="16">
+    <row r="159" spans="1:2" ht="15">
       <c r="A159" s="2" t="s">
         <v>56</v>
       </c>
@@ -3171,7 +3741,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="16">
+    <row r="160" spans="1:2" ht="15">
       <c r="A160" s="2" t="s">
         <v>309</v>
       </c>
@@ -3179,7 +3749,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="16">
+    <row r="161" spans="1:2" ht="15">
       <c r="A161" s="2" t="s">
         <v>310</v>
       </c>
@@ -3187,7 +3757,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="16">
+    <row r="162" spans="1:2" ht="15">
       <c r="A162" s="2" t="s">
         <v>311</v>
       </c>
@@ -3195,7 +3765,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="16">
+    <row r="163" spans="1:2" ht="15">
       <c r="A163" s="2" t="s">
         <v>312</v>
       </c>
@@ -3203,7 +3773,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="16">
+    <row r="164" spans="1:2" ht="15">
       <c r="A164" s="2" t="s">
         <v>313</v>
       </c>
@@ -3211,7 +3781,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="16">
+    <row r="165" spans="1:2" ht="15">
       <c r="A165" s="2" t="s">
         <v>314</v>
       </c>
@@ -3219,7 +3789,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="16">
+    <row r="166" spans="1:2" ht="15">
       <c r="A166" s="2" t="s">
         <v>315</v>
       </c>
@@ -3227,7 +3797,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="16">
+    <row r="167" spans="1:2" ht="15">
       <c r="A167" s="2" t="s">
         <v>316</v>
       </c>
@@ -3235,7 +3805,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="16">
+    <row r="168" spans="1:2" ht="15">
       <c r="A168" s="2" t="s">
         <v>317</v>
       </c>
@@ -3243,7 +3813,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="16">
+    <row r="169" spans="1:2" ht="15">
       <c r="A169" s="2" t="s">
         <v>333</v>
       </c>
@@ -3251,7 +3821,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="16">
+    <row r="170" spans="1:2" ht="15">
       <c r="A170" s="2" t="s">
         <v>335</v>
       </c>
@@ -3259,7 +3829,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="16">
+    <row r="171" spans="1:2" ht="15">
       <c r="A171" s="2" t="s">
         <v>337</v>
       </c>
@@ -3267,7 +3837,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="16">
+    <row r="172" spans="1:2" ht="15">
       <c r="A172" s="2" t="s">
         <v>339</v>
       </c>
@@ -3275,7 +3845,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="16">
+    <row r="173" spans="1:2" ht="15">
       <c r="A173" s="2" t="s">
         <v>341</v>
       </c>
@@ -3283,7 +3853,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="16">
+    <row r="174" spans="1:2" ht="15">
       <c r="A174" s="2" t="s">
         <v>343</v>
       </c>
@@ -3291,7 +3861,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="16">
+    <row r="175" spans="1:2" ht="15">
       <c r="A175" s="2" t="s">
         <v>345</v>
       </c>
@@ -3299,7 +3869,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="16">
+    <row r="176" spans="1:2" ht="15">
       <c r="A176" s="2" t="s">
         <v>347</v>
       </c>
@@ -3307,7 +3877,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="16">
+    <row r="177" spans="1:2" ht="15">
       <c r="A177" s="2" t="s">
         <v>200</v>
       </c>
@@ -3315,7 +3885,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="16">
+    <row r="178" spans="1:2" ht="15">
       <c r="A178" s="2" t="s">
         <v>349</v>
       </c>
@@ -3323,7 +3893,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="16">
+    <row r="179" spans="1:2" ht="15">
       <c r="A179" s="2" t="s">
         <v>351</v>
       </c>
@@ -3331,7 +3901,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="16">
+    <row r="180" spans="1:2" ht="15">
       <c r="A180" s="2" t="s">
         <v>353</v>
       </c>
@@ -3339,7 +3909,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="16">
+    <row r="181" spans="1:2" ht="15">
       <c r="A181" s="2" t="s">
         <v>355</v>
       </c>
@@ -3347,7 +3917,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="16">
+    <row r="182" spans="1:2" ht="15">
       <c r="A182" s="2" t="s">
         <v>357</v>
       </c>
@@ -3355,7 +3925,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="16">
+    <row r="183" spans="1:2" ht="15">
       <c r="A183" s="2" t="s">
         <v>359</v>
       </c>
@@ -3363,7 +3933,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="16">
+    <row r="184" spans="1:2" ht="15">
       <c r="A184" s="2" t="s">
         <v>361</v>
       </c>
@@ -3371,7 +3941,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="16">
+    <row r="185" spans="1:2" ht="15">
       <c r="A185" s="2" t="s">
         <v>363</v>
       </c>
@@ -3379,7 +3949,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="16">
+    <row r="186" spans="1:2" ht="15">
       <c r="A186" s="2" t="s">
         <v>365</v>
       </c>
@@ -3387,7 +3957,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="16">
+    <row r="187" spans="1:2" ht="15">
       <c r="A187" s="2" t="s">
         <v>367</v>
       </c>
@@ -3395,7 +3965,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="16">
+    <row r="188" spans="1:2" ht="15">
       <c r="A188" s="2" t="s">
         <v>369</v>
       </c>
@@ -3403,7 +3973,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="16">
+    <row r="189" spans="1:2" ht="15">
       <c r="A189" s="2" t="s">
         <v>371</v>
       </c>
@@ -3411,7 +3981,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="16">
+    <row r="190" spans="1:2" ht="15">
       <c r="A190" s="2" t="s">
         <v>373</v>
       </c>
@@ -3419,7 +3989,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="16">
+    <row r="191" spans="1:2" ht="15">
       <c r="A191" s="2" t="s">
         <v>375</v>
       </c>
@@ -3427,7 +3997,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="16">
+    <row r="192" spans="1:2" ht="15">
       <c r="A192" s="2" t="s">
         <v>377</v>
       </c>
@@ -3435,7 +4005,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="16">
+    <row r="193" spans="1:2" ht="15">
       <c r="A193" s="2" t="s">
         <v>379</v>
       </c>
@@ -3443,7 +4013,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="16">
+    <row r="194" spans="1:2" ht="15">
       <c r="A194" s="2" t="s">
         <v>380</v>
       </c>
@@ -3451,7 +4021,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="16">
+    <row r="195" spans="1:2" ht="15">
       <c r="A195" s="2" t="s">
         <v>382</v>
       </c>
@@ -3459,7 +4029,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="16">
+    <row r="196" spans="1:2" ht="15">
       <c r="A196" s="2" t="s">
         <v>384</v>
       </c>
@@ -3467,7 +4037,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="16">
+    <row r="197" spans="1:2" ht="15">
       <c r="A197" s="2" t="s">
         <v>386</v>
       </c>
@@ -3475,7 +4045,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="16">
+    <row r="198" spans="1:2" ht="15">
       <c r="A198" s="2" t="s">
         <v>388</v>
       </c>
@@ -3483,7 +4053,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="16">
+    <row r="199" spans="1:2" ht="15">
       <c r="A199" s="2" t="s">
         <v>390</v>
       </c>
@@ -3491,7 +4061,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="16">
+    <row r="200" spans="1:2" ht="15">
       <c r="A200" s="2" t="s">
         <v>392</v>
       </c>
@@ -3499,7 +4069,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="16">
+    <row r="201" spans="1:2" ht="15">
       <c r="A201" s="2" t="s">
         <v>394</v>
       </c>
@@ -3507,7 +4077,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="16">
+    <row r="202" spans="1:2" ht="15">
       <c r="A202" s="2" t="s">
         <v>396</v>
       </c>
@@ -3515,7 +4085,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="16">
+    <row r="203" spans="1:2" ht="15">
       <c r="A203" s="2" t="s">
         <v>398</v>
       </c>
@@ -3523,7 +4093,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="16">
+    <row r="204" spans="1:2" ht="15">
       <c r="A204" s="2" t="s">
         <v>400</v>
       </c>
@@ -3531,7 +4101,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="16">
+    <row r="205" spans="1:2" ht="15">
       <c r="A205" s="2" t="s">
         <v>402</v>
       </c>
@@ -3539,7 +4109,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="16">
+    <row r="206" spans="1:2" ht="15">
       <c r="A206" s="2" t="s">
         <v>404</v>
       </c>
@@ -3547,7 +4117,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="16">
+    <row r="207" spans="1:2" ht="15">
       <c r="A207" s="2" t="s">
         <v>406</v>
       </c>
@@ -3555,7 +4125,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="16">
+    <row r="208" spans="1:2" ht="15">
       <c r="A208" s="2" t="s">
         <v>206</v>
       </c>
@@ -3563,7 +4133,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="16">
+    <row r="209" spans="1:2" ht="15">
       <c r="A209" s="2" t="s">
         <v>408</v>
       </c>
@@ -3571,7 +4141,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="16">
+    <row r="210" spans="1:2" ht="15">
       <c r="A210" s="2" t="s">
         <v>410</v>
       </c>
@@ -3579,7 +4149,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="16">
+    <row r="211" spans="1:2" ht="15">
       <c r="A211" s="2" t="s">
         <v>412</v>
       </c>
@@ -3587,7 +4157,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="16">
+    <row r="212" spans="1:2" ht="15">
       <c r="A212" s="2" t="s">
         <v>414</v>
       </c>
@@ -3595,7 +4165,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="16">
+    <row r="213" spans="1:2" ht="15">
       <c r="A213" s="2" t="s">
         <v>416</v>
       </c>
@@ -3603,7 +4173,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="16">
+    <row r="214" spans="1:2" ht="15">
       <c r="A214" s="2" t="s">
         <v>418</v>
       </c>
@@ -3611,7 +4181,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="16">
+    <row r="215" spans="1:2" ht="15">
       <c r="A215" s="2" t="s">
         <v>420</v>
       </c>
@@ -3619,7 +4189,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="16">
+    <row r="216" spans="1:2" ht="15">
       <c r="A216" s="2" t="s">
         <v>422</v>
       </c>
@@ -3627,7 +4197,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="16">
+    <row r="217" spans="1:2" ht="15">
       <c r="A217" s="2" t="s">
         <v>424</v>
       </c>
@@ -3635,7 +4205,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="16">
+    <row r="218" spans="1:2" ht="15">
       <c r="A218" s="2" t="s">
         <v>426</v>
       </c>
@@ -3643,7 +4213,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="16">
+    <row r="219" spans="1:2" ht="15">
       <c r="A219" s="2" t="s">
         <v>158</v>
       </c>
@@ -3651,7 +4221,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="16">
+    <row r="220" spans="1:2" ht="15">
       <c r="A220" s="2" t="s">
         <v>428</v>
       </c>
@@ -3659,7 +4229,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="16">
+    <row r="221" spans="1:2" ht="15">
       <c r="A221" s="2" t="s">
         <v>221</v>
       </c>
@@ -3667,7 +4237,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="16">
+    <row r="222" spans="1:2" ht="15">
       <c r="A222" s="2" t="s">
         <v>430</v>
       </c>
@@ -3675,7 +4245,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="16">
+    <row r="223" spans="1:2" ht="15">
       <c r="A223" s="2" t="s">
         <v>432</v>
       </c>
@@ -3683,7 +4253,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="16">
+    <row r="224" spans="1:2" ht="15">
       <c r="A224" s="2" t="s">
         <v>434</v>
       </c>
@@ -3691,7 +4261,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="16">
+    <row r="225" spans="1:2" ht="15">
       <c r="A225" s="2" t="s">
         <v>436</v>
       </c>
@@ -3699,7 +4269,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="16">
+    <row r="226" spans="1:2" ht="15">
       <c r="A226" s="2" t="s">
         <v>438</v>
       </c>
@@ -3707,7 +4277,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="16">
+    <row r="227" spans="1:2" ht="15">
       <c r="A227" s="2" t="s">
         <v>440</v>
       </c>
@@ -3715,7 +4285,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="16">
+    <row r="228" spans="1:2" ht="15">
       <c r="A228" s="2" t="s">
         <v>442</v>
       </c>
@@ -3723,7 +4293,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="16">
+    <row r="229" spans="1:2" ht="15">
       <c r="A229" s="2" t="s">
         <v>444</v>
       </c>
@@ -3731,7 +4301,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="16">
+    <row r="230" spans="1:2" ht="15">
       <c r="A230" s="2" t="s">
         <v>446</v>
       </c>
@@ -3739,7 +4309,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="16">
+    <row r="231" spans="1:2" ht="15">
       <c r="A231" s="2" t="s">
         <v>448</v>
       </c>
@@ -3747,7 +4317,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="16">
+    <row r="232" spans="1:2" ht="15">
       <c r="A232" s="2" t="s">
         <v>450</v>
       </c>
@@ -3755,7 +4325,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="16">
+    <row r="233" spans="1:2" ht="15">
       <c r="A233" s="2" t="s">
         <v>452</v>
       </c>
@@ -3763,7 +4333,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="16">
+    <row r="234" spans="1:2" ht="15">
       <c r="A234" s="2" t="s">
         <v>454</v>
       </c>
@@ -3771,7 +4341,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="16">
+    <row r="235" spans="1:2" ht="15">
       <c r="A235" s="2" t="s">
         <v>456</v>
       </c>
@@ -3779,7 +4349,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="16">
+    <row r="236" spans="1:2" ht="15">
       <c r="A236" s="2" t="s">
         <v>458</v>
       </c>
@@ -3787,7 +4357,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="16">
+    <row r="237" spans="1:2" ht="15">
       <c r="A237" s="2" t="s">
         <v>460</v>
       </c>
@@ -3795,7 +4365,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="16">
+    <row r="238" spans="1:2" ht="15">
       <c r="A238" s="2" t="s">
         <v>462</v>
       </c>
@@ -3803,7 +4373,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="16">
+    <row r="239" spans="1:2" ht="15">
       <c r="A239" s="2" t="s">
         <v>464</v>
       </c>
@@ -3811,7 +4381,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="16">
+    <row r="240" spans="1:2" ht="15">
       <c r="A240" s="2" t="s">
         <v>466</v>
       </c>
@@ -3819,7 +4389,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="16">
+    <row r="241" spans="1:2" ht="15">
       <c r="A241" s="2" t="s">
         <v>468</v>
       </c>
@@ -3827,7 +4397,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="16">
+    <row r="242" spans="1:2" ht="15">
       <c r="A242" s="2" t="s">
         <v>161</v>
       </c>
@@ -3835,7 +4405,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="16">
+    <row r="243" spans="1:2" ht="15">
       <c r="A243" s="2" t="s">
         <v>470</v>
       </c>
@@ -3843,7 +4413,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="16">
+    <row r="244" spans="1:2" ht="15">
       <c r="A244" s="2" t="s">
         <v>472</v>
       </c>
@@ -3851,7 +4421,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="16">
+    <row r="245" spans="1:2" ht="15">
       <c r="A245" s="2" t="s">
         <v>156</v>
       </c>
@@ -3859,7 +4429,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="16">
+    <row r="246" spans="1:2" ht="15">
       <c r="A246" s="2" t="s">
         <v>474</v>
       </c>
@@ -3867,7 +4437,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="16">
+    <row r="247" spans="1:2" ht="15">
       <c r="A247" s="2" t="s">
         <v>205</v>
       </c>
@@ -3875,7 +4445,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="16">
+    <row r="248" spans="1:2" ht="15">
       <c r="A248" s="2" t="s">
         <v>476</v>
       </c>
@@ -3883,7 +4453,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="16">
+    <row r="249" spans="1:2" ht="15">
       <c r="A249" s="2" t="s">
         <v>478</v>
       </c>
@@ -3891,7 +4461,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="16">
+    <row r="250" spans="1:2" ht="15">
       <c r="A250" s="2" t="s">
         <v>152</v>
       </c>
@@ -3899,7 +4469,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="16">
+    <row r="251" spans="1:2" ht="15">
       <c r="A251" s="2" t="s">
         <v>480</v>
       </c>
@@ -3907,7 +4477,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="16">
+    <row r="252" spans="1:2" ht="15">
       <c r="A252" s="2" t="s">
         <v>482</v>
       </c>
@@ -3915,7 +4485,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="16">
+    <row r="253" spans="1:2" ht="15">
       <c r="A253" s="2" t="s">
         <v>484</v>
       </c>
@@ -3923,7 +4493,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="16">
+    <row r="254" spans="1:2" ht="15">
       <c r="A254" s="2" t="s">
         <v>486</v>
       </c>
@@ -3931,7 +4501,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="16">
+    <row r="255" spans="1:2" ht="15">
       <c r="A255" s="2" t="s">
         <v>488</v>
       </c>
@@ -3939,7 +4509,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="16">
+    <row r="256" spans="1:2" ht="15">
       <c r="A256" s="2" t="s">
         <v>490</v>
       </c>
@@ -3947,7 +4517,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="16">
+    <row r="257" spans="1:2" ht="15">
       <c r="A257" s="2" t="s">
         <v>492</v>
       </c>
@@ -3955,7 +4525,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="16">
+    <row r="258" spans="1:2" ht="15">
       <c r="A258" s="2" t="s">
         <v>494</v>
       </c>
@@ -3963,7 +4533,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="16">
+    <row r="259" spans="1:2" ht="15">
       <c r="A259" s="2" t="s">
         <v>496</v>
       </c>
@@ -3971,7 +4541,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="16">
+    <row r="260" spans="1:2" ht="15">
       <c r="A260" s="2" t="s">
         <v>498</v>
       </c>
@@ -3979,7 +4549,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="16">
+    <row r="261" spans="1:2" ht="15">
       <c r="A261" s="2" t="s">
         <v>500</v>
       </c>
@@ -3987,7 +4557,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="32">
+    <row r="262" spans="1:2" ht="15">
       <c r="A262" s="2" t="s">
         <v>157</v>
       </c>
@@ -3995,7 +4565,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="16">
+    <row r="263" spans="1:2" ht="15">
       <c r="A263" s="2" t="s">
         <v>503</v>
       </c>
@@ -4003,7 +4573,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="16">
+    <row r="264" spans="1:2" ht="15">
       <c r="A264" s="2" t="s">
         <v>505</v>
       </c>
@@ -4011,7 +4581,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="16">
+    <row r="265" spans="1:2" ht="15">
       <c r="A265" s="2" t="s">
         <v>507</v>
       </c>
@@ -4019,7 +4589,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="16">
+    <row r="266" spans="1:2" ht="15">
       <c r="A266" s="2" t="s">
         <v>509</v>
       </c>
@@ -4027,7 +4597,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="16">
+    <row r="267" spans="1:2" ht="15">
       <c r="A267" s="2" t="s">
         <v>511</v>
       </c>
@@ -4035,7 +4605,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="16">
+    <row r="268" spans="1:2" ht="15">
       <c r="A268" s="2" t="s">
         <v>513</v>
       </c>
@@ -4043,7 +4613,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="16">
+    <row r="269" spans="1:2" ht="15">
       <c r="A269" s="2" t="s">
         <v>515</v>
       </c>
@@ -4051,7 +4621,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="16">
+    <row r="270" spans="1:2" ht="15">
       <c r="A270" s="2" t="s">
         <v>517</v>
       </c>
@@ -4059,7 +4629,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="16">
+    <row r="271" spans="1:2" ht="15">
       <c r="A271" s="2" t="s">
         <v>519</v>
       </c>
@@ -4067,7 +4637,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="16">
+    <row r="272" spans="1:2" ht="15">
       <c r="A272" s="2" t="s">
         <v>521</v>
       </c>
@@ -4075,7 +4645,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="16">
+    <row r="273" spans="1:2" ht="15">
       <c r="A273" s="2" t="s">
         <v>523</v>
       </c>
@@ -4083,7 +4653,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="16">
+    <row r="274" spans="1:2" ht="15">
       <c r="A274" s="2" t="s">
         <v>525</v>
       </c>
@@ -4091,7 +4661,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="16">
+    <row r="275" spans="1:2" ht="15">
       <c r="A275" s="2" t="s">
         <v>170</v>
       </c>
@@ -4099,7 +4669,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="16">
+    <row r="276" spans="1:2" ht="15">
       <c r="A276" s="2" t="s">
         <v>527</v>
       </c>
@@ -4107,7 +4677,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="16">
+    <row r="277" spans="1:2" ht="15">
       <c r="A277" s="2" t="s">
         <v>529</v>
       </c>
@@ -4115,7 +4685,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="16">
+    <row r="278" spans="1:2" ht="15">
       <c r="A278" s="2" t="s">
         <v>531</v>
       </c>
@@ -4123,7 +4693,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="16">
+    <row r="279" spans="1:2" ht="15">
       <c r="A279" s="2" t="s">
         <v>533</v>
       </c>
@@ -4131,7 +4701,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="16">
+    <row r="280" spans="1:2" ht="15">
       <c r="A280" s="2" t="s">
         <v>535</v>
       </c>
@@ -4139,7 +4709,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="16">
+    <row r="281" spans="1:2" ht="15">
       <c r="A281" s="2" t="s">
         <v>199</v>
       </c>
@@ -4147,7 +4717,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="16">
+    <row r="282" spans="1:2" ht="15">
       <c r="A282" s="2" t="s">
         <v>537</v>
       </c>
@@ -4155,7 +4725,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="16">
+    <row r="283" spans="1:2" ht="15">
       <c r="A283" s="2" t="s">
         <v>539</v>
       </c>
@@ -4163,7 +4733,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="16">
+    <row r="284" spans="1:2" ht="15">
       <c r="A284" s="2" t="s">
         <v>541</v>
       </c>
@@ -4171,7 +4741,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="16">
+    <row r="285" spans="1:2" ht="15">
       <c r="A285" s="2" t="s">
         <v>543</v>
       </c>
@@ -4179,7 +4749,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="16">
+    <row r="286" spans="1:2" ht="15">
       <c r="A286" s="2" t="s">
         <v>545</v>
       </c>
@@ -4187,7 +4757,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="16">
+    <row r="287" spans="1:2" ht="15">
       <c r="A287" s="2" t="s">
         <v>547</v>
       </c>
@@ -4195,7 +4765,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="16">
+    <row r="288" spans="1:2" ht="15">
       <c r="A288" s="2" t="s">
         <v>549</v>
       </c>
@@ -4203,405 +4773,805 @@
         <v>550</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
-      <c r="A289" s="3"/>
-      <c r="B289" s="3"/>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290" s="3"/>
-      <c r="B290" s="3"/>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" s="3"/>
-      <c r="B291" s="3"/>
-    </row>
-    <row r="292" spans="1:2">
-      <c r="A292" s="3"/>
-      <c r="B292" s="3"/>
-    </row>
-    <row r="293" spans="1:2">
-      <c r="A293" s="3"/>
-      <c r="B293" s="3"/>
-    </row>
-    <row r="294" spans="1:2">
-      <c r="A294" s="3"/>
-      <c r="B294" s="3"/>
-    </row>
-    <row r="295" spans="1:2">
-      <c r="A295" s="3"/>
-      <c r="B295" s="3"/>
-    </row>
-    <row r="296" spans="1:2">
-      <c r="A296" s="3"/>
-      <c r="B296" s="3"/>
-    </row>
-    <row r="297" spans="1:2">
-      <c r="A297" s="3"/>
-      <c r="B297" s="3"/>
-    </row>
-    <row r="298" spans="1:2">
-      <c r="A298" s="3"/>
-      <c r="B298" s="3"/>
-    </row>
-    <row r="299" spans="1:2">
-      <c r="A299" s="3"/>
-      <c r="B299" s="3"/>
-    </row>
-    <row r="300" spans="1:2">
-      <c r="A300" s="3"/>
-      <c r="B300" s="3"/>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301" s="3"/>
-      <c r="B301" s="3"/>
-    </row>
-    <row r="302" spans="1:2">
-      <c r="A302" s="3"/>
-      <c r="B302" s="3"/>
-    </row>
-    <row r="303" spans="1:2">
-      <c r="A303" s="3"/>
-      <c r="B303" s="3"/>
-    </row>
-    <row r="304" spans="1:2">
-      <c r="A304" s="3"/>
-      <c r="B304" s="3"/>
-    </row>
-    <row r="305" spans="1:2">
-      <c r="A305" s="3"/>
-      <c r="B305" s="3"/>
-    </row>
-    <row r="306" spans="1:2">
-      <c r="A306" s="3"/>
-      <c r="B306" s="3"/>
-    </row>
-    <row r="307" spans="1:2">
-      <c r="A307" s="3"/>
-      <c r="B307" s="3"/>
-    </row>
-    <row r="308" spans="1:2">
-      <c r="A308" s="3"/>
-      <c r="B308" s="3"/>
-    </row>
-    <row r="309" spans="1:2">
-      <c r="A309" s="3"/>
-      <c r="B309" s="3"/>
-    </row>
-    <row r="310" spans="1:2">
-      <c r="A310" s="3"/>
-      <c r="B310" s="3"/>
-    </row>
-    <row r="311" spans="1:2">
-      <c r="A311" s="3"/>
-      <c r="B311" s="3"/>
-    </row>
-    <row r="312" spans="1:2">
-      <c r="A312" s="3"/>
-      <c r="B312" s="3"/>
-    </row>
-    <row r="313" spans="1:2">
-      <c r="A313" s="3"/>
-      <c r="B313" s="3"/>
-    </row>
-    <row r="314" spans="1:2">
-      <c r="A314" s="3"/>
-      <c r="B314" s="3"/>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="A315" s="3"/>
-      <c r="B315" s="3"/>
-    </row>
-    <row r="316" spans="1:2">
-      <c r="A316" s="3"/>
-      <c r="B316" s="3"/>
-    </row>
-    <row r="317" spans="1:2">
-      <c r="A317" s="3"/>
-      <c r="B317" s="3"/>
-    </row>
-    <row r="318" spans="1:2">
-      <c r="A318" s="3"/>
-      <c r="B318" s="3"/>
-    </row>
-    <row r="319" spans="1:2">
-      <c r="A319" s="3"/>
-      <c r="B319" s="3"/>
-    </row>
-    <row r="320" spans="1:2">
-      <c r="A320" s="3"/>
-      <c r="B320" s="3"/>
-    </row>
-    <row r="321" spans="1:2">
-      <c r="A321" s="3"/>
-      <c r="B321" s="3"/>
-    </row>
-    <row r="322" spans="1:2">
-      <c r="A322" s="3"/>
-      <c r="B322" s="3"/>
-    </row>
-    <row r="323" spans="1:2">
-      <c r="A323" s="3"/>
-      <c r="B323" s="3"/>
-    </row>
-    <row r="324" spans="1:2">
-      <c r="A324" s="3"/>
-      <c r="B324" s="3"/>
-    </row>
-    <row r="325" spans="1:2">
-      <c r="A325" s="3"/>
-      <c r="B325" s="3"/>
-    </row>
-    <row r="326" spans="1:2">
-      <c r="A326" s="3"/>
-      <c r="B326" s="3"/>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="A327" s="3"/>
-      <c r="B327" s="3"/>
-    </row>
-    <row r="328" spans="1:2">
-      <c r="A328" s="3"/>
-      <c r="B328" s="3"/>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" s="3"/>
-      <c r="B329" s="3"/>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" s="3"/>
-      <c r="B330" s="3"/>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" s="3"/>
-      <c r="B331" s="3"/>
-    </row>
-    <row r="332" spans="1:2">
-      <c r="A332" s="3"/>
-      <c r="B332" s="3"/>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" s="3"/>
-      <c r="B333" s="3"/>
-    </row>
-    <row r="334" spans="1:2">
-      <c r="A334" s="3"/>
-      <c r="B334" s="3"/>
-    </row>
-    <row r="335" spans="1:2">
-      <c r="A335" s="3"/>
-      <c r="B335" s="3"/>
-    </row>
-    <row r="336" spans="1:2">
-      <c r="A336" s="3"/>
-      <c r="B336" s="3"/>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="A337" s="3"/>
-      <c r="B337" s="3"/>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" s="3"/>
-      <c r="B338" s="3"/>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" s="3"/>
-      <c r="B339" s="3"/>
-    </row>
-    <row r="340" spans="1:2">
-      <c r="A340" s="3"/>
-      <c r="B340" s="3"/>
-    </row>
-    <row r="341" spans="1:2">
-      <c r="A341" s="3"/>
-      <c r="B341" s="3"/>
-    </row>
-    <row r="342" spans="1:2">
-      <c r="A342" s="3"/>
-      <c r="B342" s="3"/>
-    </row>
-    <row r="343" spans="1:2">
-      <c r="A343" s="3"/>
-      <c r="B343" s="3"/>
-    </row>
-    <row r="344" spans="1:2">
-      <c r="A344" s="3"/>
-      <c r="B344" s="3"/>
-    </row>
-    <row r="345" spans="1:2">
-      <c r="A345" s="3"/>
-      <c r="B345" s="3"/>
-    </row>
-    <row r="346" spans="1:2">
-      <c r="A346" s="3"/>
-      <c r="B346" s="3"/>
-    </row>
-    <row r="347" spans="1:2">
-      <c r="A347" s="3"/>
-      <c r="B347" s="3"/>
-    </row>
-    <row r="348" spans="1:2">
-      <c r="A348" s="3"/>
-      <c r="B348" s="3"/>
-    </row>
-    <row r="349" spans="1:2">
-      <c r="A349" s="3"/>
-      <c r="B349" s="3"/>
-    </row>
-    <row r="350" spans="1:2">
-      <c r="A350" s="3"/>
-      <c r="B350" s="3"/>
-    </row>
-    <row r="351" spans="1:2">
-      <c r="A351" s="3"/>
-      <c r="B351" s="3"/>
-    </row>
-    <row r="352" spans="1:2">
-      <c r="A352" s="3"/>
-      <c r="B352" s="3"/>
-    </row>
-    <row r="353" spans="1:2">
-      <c r="A353" s="3"/>
-      <c r="B353" s="3"/>
-    </row>
-    <row r="354" spans="1:2">
-      <c r="A354" s="3"/>
-      <c r="B354" s="3"/>
-    </row>
-    <row r="355" spans="1:2">
-      <c r="A355" s="3"/>
-      <c r="B355" s="3"/>
-    </row>
-    <row r="356" spans="1:2">
-      <c r="A356" s="3"/>
-      <c r="B356" s="3"/>
-    </row>
-    <row r="357" spans="1:2">
-      <c r="A357" s="3"/>
-      <c r="B357" s="3"/>
-    </row>
-    <row r="358" spans="1:2">
-      <c r="A358" s="3"/>
-      <c r="B358" s="3"/>
-    </row>
-    <row r="359" spans="1:2">
-      <c r="A359" s="3"/>
-      <c r="B359" s="3"/>
-    </row>
-    <row r="360" spans="1:2">
-      <c r="A360" s="3"/>
-      <c r="B360" s="3"/>
-    </row>
-    <row r="361" spans="1:2">
-      <c r="A361" s="3"/>
-      <c r="B361" s="3"/>
-    </row>
-    <row r="362" spans="1:2">
-      <c r="A362" s="3"/>
-      <c r="B362" s="3"/>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" s="3"/>
-      <c r="B363" s="3"/>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="A364" s="3"/>
-      <c r="B364" s="3"/>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="A365" s="3"/>
-      <c r="B365" s="3"/>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" s="3"/>
-      <c r="B366" s="3"/>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" s="3"/>
-      <c r="B367" s="3"/>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" s="3"/>
-      <c r="B368" s="3"/>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" s="3"/>
-      <c r="B369" s="3"/>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" s="3"/>
-      <c r="B370" s="3"/>
-    </row>
-    <row r="371" spans="1:2">
-      <c r="A371" s="3"/>
-      <c r="B371" s="3"/>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" s="3"/>
-      <c r="B372" s="3"/>
-    </row>
-    <row r="373" spans="1:2">
-      <c r="A373" s="3"/>
-      <c r="B373" s="3"/>
-    </row>
-    <row r="374" spans="1:2">
-      <c r="A374" s="3"/>
-      <c r="B374" s="3"/>
-    </row>
-    <row r="375" spans="1:2">
-      <c r="A375" s="3"/>
-      <c r="B375" s="3"/>
-    </row>
-    <row r="376" spans="1:2">
-      <c r="A376" s="3"/>
-      <c r="B376" s="3"/>
-    </row>
-    <row r="377" spans="1:2">
-      <c r="A377" s="3"/>
-      <c r="B377" s="3"/>
-    </row>
-    <row r="378" spans="1:2">
-      <c r="A378" s="3"/>
-      <c r="B378" s="3"/>
-    </row>
-    <row r="379" spans="1:2">
-      <c r="A379" s="3"/>
-      <c r="B379" s="3"/>
-    </row>
-    <row r="380" spans="1:2">
-      <c r="A380" s="3"/>
-      <c r="B380" s="3"/>
-    </row>
-    <row r="381" spans="1:2">
-      <c r="A381" s="3"/>
-      <c r="B381" s="3"/>
-    </row>
-    <row r="382" spans="1:2">
-      <c r="A382" s="3"/>
-      <c r="B382" s="3"/>
-    </row>
-    <row r="383" spans="1:2">
-      <c r="A383" s="3"/>
-      <c r="B383" s="3"/>
-    </row>
-    <row r="384" spans="1:2">
-      <c r="A384" s="3"/>
-      <c r="B384" s="3"/>
-    </row>
-    <row r="385" spans="1:2">
-      <c r="A385" s="3"/>
-      <c r="B385" s="3"/>
-    </row>
-    <row r="386" spans="1:2">
-      <c r="A386" s="3"/>
-      <c r="B386" s="3"/>
-    </row>
-    <row r="387" spans="1:2">
-      <c r="A387" s="3"/>
-      <c r="B387" s="3"/>
-    </row>
-    <row r="388" spans="1:2">
-      <c r="A388" s="3"/>
-      <c r="B388" s="3"/>
+    <row r="289" spans="1:2" ht="15">
+      <c r="A289" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" ht="15">
+      <c r="A290" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" ht="15">
+      <c r="A291" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" ht="15">
+      <c r="A292" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" ht="15">
+      <c r="A293" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" ht="15">
+      <c r="A294" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="15">
+      <c r="A295" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" ht="15">
+      <c r="A296" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" ht="15">
+      <c r="A297" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" ht="15">
+      <c r="A298" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" ht="15">
+      <c r="A299" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" ht="15">
+      <c r="A300" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" ht="15">
+      <c r="A301" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" ht="15">
+      <c r="A302" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" ht="15">
+      <c r="A303" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" ht="15">
+      <c r="A304" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" ht="15">
+      <c r="A305" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" ht="15">
+      <c r="A306" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" ht="15">
+      <c r="A307" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="15">
+      <c r="A308" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="15">
+      <c r="A309" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" ht="15">
+      <c r="A310" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" ht="15">
+      <c r="A311" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" ht="15">
+      <c r="A312" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" ht="15">
+      <c r="A313" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" ht="15">
+      <c r="A314" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" ht="15">
+      <c r="A315" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" ht="15">
+      <c r="A316" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" ht="15">
+      <c r="A317" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" ht="15">
+      <c r="A318" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" ht="15">
+      <c r="A319" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" ht="15">
+      <c r="A320" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" ht="15">
+      <c r="A321" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" ht="15">
+      <c r="A322" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" ht="15">
+      <c r="A323" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" ht="15">
+      <c r="A324" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" ht="15">
+      <c r="A325" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" ht="15">
+      <c r="A326" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" ht="15">
+      <c r="A327" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" ht="15">
+      <c r="A328" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" ht="15">
+      <c r="A329" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" ht="15">
+      <c r="A330" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" ht="15">
+      <c r="A331" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" ht="15">
+      <c r="A332" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" ht="15">
+      <c r="A333" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" ht="15">
+      <c r="A334" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" ht="15">
+      <c r="A335" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" ht="15">
+      <c r="A336" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" ht="15">
+      <c r="A337" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" ht="15">
+      <c r="A338" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" ht="15">
+      <c r="A339" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" ht="15">
+      <c r="A340" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" ht="15">
+      <c r="A341" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" ht="15">
+      <c r="A342" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" ht="15">
+      <c r="A343" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" ht="15">
+      <c r="A344" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" ht="15">
+      <c r="A345" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" ht="15">
+      <c r="A346" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" ht="15">
+      <c r="A347" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" ht="15">
+      <c r="A348" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" ht="15">
+      <c r="A349" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" ht="15">
+      <c r="A350" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" ht="15">
+      <c r="A351" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" ht="15">
+      <c r="A352" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" ht="15">
+      <c r="A353" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" ht="15">
+      <c r="A354" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" ht="15">
+      <c r="A355" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" ht="15">
+      <c r="A356" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" ht="15">
+      <c r="A357" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" ht="15">
+      <c r="A358" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" ht="15">
+      <c r="A359" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" ht="15">
+      <c r="A360" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" ht="15">
+      <c r="A361" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" ht="15">
+      <c r="A362" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" ht="15">
+      <c r="A363" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" ht="15">
+      <c r="A364" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" ht="15">
+      <c r="A365" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" ht="15">
+      <c r="A366" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" ht="15">
+      <c r="A367" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" ht="15">
+      <c r="A368" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" ht="15">
+      <c r="A369" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" ht="15">
+      <c r="A370" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" ht="15">
+      <c r="A371" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" ht="15">
+      <c r="A372" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" ht="15">
+      <c r="A373" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" ht="15">
+      <c r="A374" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" ht="15">
+      <c r="A375" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" ht="15">
+      <c r="A376" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" ht="15">
+      <c r="A377" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" ht="15">
+      <c r="A378" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" ht="15">
+      <c r="A379" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" ht="15">
+      <c r="A380" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" ht="15">
+      <c r="A381" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" ht="15">
+      <c r="A382" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" ht="15">
+      <c r="A383" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" ht="15">
+      <c r="A384" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" ht="15">
+      <c r="A385" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" ht="15">
+      <c r="A386" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" ht="15">
+      <c r="A387" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" ht="15">
+      <c r="A388" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>740</v>
+      </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" s="3"/>
